--- a/Misc/Calculations for new boost converter.xlsx
+++ b/Misc/Calculations for new boost converter.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://mcmasteru365-my.sharepoint.com/personal/martio6_mcmaster_ca/Documents/Rocketry/KiCAD/Github Repos/EPS_V1/Misc/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="644" documentId="8_{F1976D24-9999-43FB-86C4-F03AA5C65DA2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2DA53CAA-2506-465A-8F74-A672EB41F556}"/>
+  <xr:revisionPtr revIDLastSave="653" documentId="8_{F1976D24-9999-43FB-86C4-F03AA5C65DA2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{63325226-7A78-409A-A8DF-8FF0C4F2F0D6}"/>
   <bookViews>
-    <workbookView xWindow="-90" yWindow="0" windowWidth="12180" windowHeight="15370" xr2:uid="{787786C2-C3C7-4949-8B8A-B8E5EF583598}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="24220" windowHeight="15500" xr2:uid="{787786C2-C3C7-4949-8B8A-B8E5EF583598}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="185" uniqueCount="122">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="187" uniqueCount="122">
   <si>
     <t>General Properties</t>
   </si>
@@ -350,12 +350,6 @@
     <t>Inductor</t>
   </si>
   <si>
-    <t>SL0420-2R2M</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://jlcpcb.com/partdetail/Techfuse-SL04202R2M/C22463806 </t>
-  </si>
-  <si>
     <t>2.2uH</t>
   </si>
   <si>
@@ -402,6 +396,12 @@
   </si>
   <si>
     <t>Inductance</t>
+  </si>
+  <si>
+    <t>SRP5030CA-2R2M</t>
+  </si>
+  <si>
+    <t>https://lcsc.com/product-detail/Power-Inductors_BOURNS-SRP5030CA-2R2M_C2046809.html?s_z=n_SRP5030CA-2R2M</t>
   </si>
 </sst>
 </file>
@@ -1719,20 +1719,20 @@
         <v>103</v>
       </c>
       <c r="B62" t="s">
-        <v>104</v>
+        <v>120</v>
       </c>
       <c r="C62" s="9" t="s">
-        <v>105</v>
+        <v>121</v>
       </c>
     </row>
     <row r="63" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B63" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
     </row>
     <row r="65" spans="1:3" ht="21" x14ac:dyDescent="0.5">
       <c r="A65" s="1" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
     </row>
     <row r="66" spans="1:3" x14ac:dyDescent="0.35">
@@ -1740,10 +1740,10 @@
         <v>90</v>
       </c>
       <c r="B66" t="s">
+        <v>106</v>
+      </c>
+      <c r="C66" s="9" t="s">
         <v>108</v>
-      </c>
-      <c r="C66" s="9" t="s">
-        <v>110</v>
       </c>
     </row>
     <row r="67" spans="1:3" x14ac:dyDescent="0.35">
@@ -1751,7 +1751,7 @@
         <v>93</v>
       </c>
       <c r="B67" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
     </row>
     <row r="69" spans="1:3" x14ac:dyDescent="0.35">
@@ -1759,10 +1759,10 @@
         <v>94</v>
       </c>
       <c r="B69" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="C69" s="9" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
     </row>
     <row r="70" spans="1:3" x14ac:dyDescent="0.35">
@@ -1770,7 +1770,7 @@
         <v>93</v>
       </c>
       <c r="B70" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
     </row>
     <row r="72" spans="1:3" x14ac:dyDescent="0.35">
@@ -1778,10 +1778,10 @@
         <v>99</v>
       </c>
       <c r="B72" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="C72" s="9" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
     </row>
     <row r="73" spans="1:3" x14ac:dyDescent="0.35">
@@ -1789,7 +1789,7 @@
         <v>93</v>
       </c>
       <c r="B73" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
     </row>
     <row r="75" spans="1:3" x14ac:dyDescent="0.35">
@@ -1897,10 +1897,10 @@
         <v>82</v>
       </c>
       <c r="B91" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="C91" s="9" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
     </row>
     <row r="92" spans="1:3" x14ac:dyDescent="0.35">
@@ -1908,7 +1908,7 @@
         <v>61</v>
       </c>
       <c r="B92" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
     </row>
     <row r="94" spans="1:3" x14ac:dyDescent="0.35">
@@ -1916,7 +1916,7 @@
         <v>86</v>
       </c>
       <c r="B94" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="C94" s="9"/>
     </row>
@@ -1929,14 +1929,19 @@
       <c r="A97" s="8" t="s">
         <v>103</v>
       </c>
-      <c r="C97" s="9"/>
+      <c r="B97" t="s">
+        <v>120</v>
+      </c>
+      <c r="C97" s="9" t="s">
+        <v>121</v>
+      </c>
     </row>
     <row r="98" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A98" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="B98" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
     </row>
   </sheetData>
@@ -1951,19 +1956,18 @@
     <hyperlink ref="C31" r:id="rId8" xr:uid="{633F3ABD-6495-4CF6-AD86-5A3A36EEEC05}"/>
     <hyperlink ref="C34" r:id="rId9" xr:uid="{38990614-DF08-4126-9035-53062EEC69B7}"/>
     <hyperlink ref="C37" r:id="rId10" xr:uid="{F7261527-1A5E-41F4-B7F7-0693ECE430F3}"/>
-    <hyperlink ref="C62" r:id="rId11" xr:uid="{9CB59FBF-31EF-45A2-B778-607C1995F5AC}"/>
-    <hyperlink ref="C75" r:id="rId12" xr:uid="{2B201239-BFC0-4CB4-A475-B4153FC98CFA}"/>
-    <hyperlink ref="C78" r:id="rId13" xr:uid="{2C19968D-3403-4FF4-AD98-E459DBDC0A57}"/>
-    <hyperlink ref="C81" r:id="rId14" xr:uid="{12563B19-7945-471D-BB67-0C5E4A372EF0}"/>
-    <hyperlink ref="C88" r:id="rId15" xr:uid="{867B3ED0-6A5F-4BE3-8E6E-F94497631E7A}"/>
-    <hyperlink ref="C84" r:id="rId16" xr:uid="{1F904BB8-7136-41C6-B6BF-0100286EF093}"/>
-    <hyperlink ref="C66" r:id="rId17" xr:uid="{312B81B4-B497-49BE-A3A1-B3DF1C2D29E6}"/>
-    <hyperlink ref="C69" r:id="rId18" xr:uid="{AF63CE5D-82CC-4D3E-9555-E213EEC678E3}"/>
-    <hyperlink ref="C91" r:id="rId19" xr:uid="{17A9F849-05CA-49BA-B331-D795EE839952}"/>
-    <hyperlink ref="C72" r:id="rId20" xr:uid="{914D706A-543C-48A7-B737-CFE0AC85C5EF}"/>
+    <hyperlink ref="C75" r:id="rId11" xr:uid="{2B201239-BFC0-4CB4-A475-B4153FC98CFA}"/>
+    <hyperlink ref="C78" r:id="rId12" xr:uid="{2C19968D-3403-4FF4-AD98-E459DBDC0A57}"/>
+    <hyperlink ref="C81" r:id="rId13" xr:uid="{12563B19-7945-471D-BB67-0C5E4A372EF0}"/>
+    <hyperlink ref="C88" r:id="rId14" xr:uid="{867B3ED0-6A5F-4BE3-8E6E-F94497631E7A}"/>
+    <hyperlink ref="C84" r:id="rId15" xr:uid="{1F904BB8-7136-41C6-B6BF-0100286EF093}"/>
+    <hyperlink ref="C66" r:id="rId16" xr:uid="{312B81B4-B497-49BE-A3A1-B3DF1C2D29E6}"/>
+    <hyperlink ref="C69" r:id="rId17" xr:uid="{AF63CE5D-82CC-4D3E-9555-E213EEC678E3}"/>
+    <hyperlink ref="C91" r:id="rId18" xr:uid="{17A9F849-05CA-49BA-B331-D795EE839952}"/>
+    <hyperlink ref="C72" r:id="rId19" xr:uid="{914D706A-543C-48A7-B737-CFE0AC85C5EF}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId21"/>
-  <drawing r:id="rId22"/>
+  <pageSetup orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId20"/>
+  <drawing r:id="rId21"/>
 </worksheet>
 </file>